--- a/rules/CORE-000738/negative/02/data/unit-test-coreid-FB1106-negative-2.xlsx
+++ b/rules/CORE-000738/negative/02/data/unit-test-coreid-FB1106-negative-2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000738\negative\02\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB11972-4248-4D31-AC1C-4DDEC5185C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1073074B-AB8C-4661-AF32-4767C803533A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="76">
   <si>
     <t>Product</t>
   </si>
@@ -267,6 +267,12 @@
   </si>
   <si>
     <t>Record</t>
+  </si>
+  <si>
+    <t>CURTRT</t>
+  </si>
+  <si>
+    <t>Current Treatment</t>
   </si>
 </sst>
 </file>
@@ -360,7 +366,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -384,10 +390,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -811,26 +814,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4AD53CD-6D08-49D1-BDDC-E7A06EC42975}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>72</v>
       </c>
     </row>
@@ -851,7 +854,7 @@
         <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -870,7 +873,44 @@
       <c r="E3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -881,7 +921,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{551C50A7-711C-4F84-8246-6B56C0451189}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="20.7109375" style="4" customWidth="1"/>
@@ -1042,7 +1082,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="7"/>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="7" t="s">
         <v>61</v>
       </c>
       <c r="F5" s="7" t="s">
@@ -1071,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="7" t="s">
         <v>63</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="10"/>
+      <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7" t="s">
         <v>26</v>
@@ -1222,7 +1262,7 @@
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -1235,21 +1275,19 @@
       <c r="D12" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>64</v>
+      <c r="E12" s="11" t="s">
+        <v>74</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>66</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="G12" s="11"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
@@ -1257,26 +1295,53 @@
         <v>17</v>
       </c>
       <c r="C13" s="7">
+        <v>5</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="7">
         <v>1</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7" t="s">
+      <c r="D14" s="7"/>
+      <c r="E14" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F14" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G14" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7" t="s">
+      <c r="H14" s="7"/>
+      <c r="I14" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J14" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K14" s="8">
         <v>44281</v>
       </c>
     </row>
@@ -1292,13 +1357,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1542,21 +1606,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1BB30A1-25F5-4D6B-AA9C-850DE868D543}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51DFFF2B-AFAE-466C-A5DC-966DF9457202}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1582,9 +1644,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51DFFF2B-AFAE-466C-A5DC-966DF9457202}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1BB30A1-25F5-4D6B-AA9C-850DE868D543}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>